--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-15.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.52</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -660,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.53</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -742,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.48</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -824,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.65</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -856,6 +872,178 @@
       </c>
       <c r="T5" t="n">
         <v>36.73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Atalanta x Pafos FC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pafos FC</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1579</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T6" t="n">
+        <v>36.73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UEFA Conference League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Freiburg x FK Jablonec</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FK Jablonec</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>889</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T7" t="n">
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>
